--- a/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
+++ b/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
+++ b/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
+++ b/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
+++ b/enrichissement-pharm/ig/ValueSet-fr-valueset-statut-du-probleme.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
